--- a/ar-collections-learning/03-validation/SME-Question-Pack-Responses.xlsx
+++ b/ar-collections-learning/03-validation/SME-Question-Pack-Responses.xlsx
@@ -11,9 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$L$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$M$138</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Questions'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Items'!$A$1:$G$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Items'!$A$1:$H$192</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Items'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -489,12 +489,13 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,30 +531,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Legacy PG proposal</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Answers items</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Blocking</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Answered by</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Attachment or notes</t>
         </is>
@@ -590,18 +596,19 @@
           <t>A new AR Collections user is setting up D365 before starting routine AR Collections work.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Favorites VG-30</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -634,18 +641,19 @@
           <t>A page does not show the information needed for collection work, such as due dates, currencies or overdue balances.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Personalized Views VG-21</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -680,16 +688,21 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Monitoring is part of the daily collection routine. Also: a weekly debt review cycle, after statements are issued, and customer or internal queries about an account. (230 §2; Part 1 Process)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>Aged Balances VG-14</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -722,18 +735,19 @@
           <t>A customer or colleague needs a copy of an invoice, or the invoice must be reviewed before contacting the customer.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Customer Invoices VG-13</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -766,18 +780,19 @@
           <t>A Collections Officer needs D365 grid data in Excel for internal analysis.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-12</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -812,16 +827,21 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>Part of the daily routine: review previous activities and make sure earlier correspondence is recorded before making new contact. (230 §2, §2.2)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>Notes and Activities VG-14</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -854,18 +874,19 @@
           <t>A Collections Officer needs to work in a legal entity other than the one that is active.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Legal Entities VG-14</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -898,18 +919,19 @@
           <t>A Collections Officer starts their collection work for the day.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Workspace VG-14</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -944,16 +966,21 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>Customer balances remain unpaid beyond agreed payment terms, after system reports or automated reminders, or at the Group Billing and Credit Manager's request. (230 Part 1 Initiation)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>Overdue Customers VG-14</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="I10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -986,18 +1013,19 @@
           <t>A Collections Officer needs to understand a customer's account before contacting them.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Customer Account VG-16</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1032,16 +1060,21 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>Immediately after customer contact by phone or email, or after any collection action that needs documenting. (230 §5)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>Collection Activities VG-16</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="I12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1074,18 +1107,19 @@
           <t>A Collections Officer needs to review a customer statement, or needs a copy of it, without sending it to the customer.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-16</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1120,16 +1154,21 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>Statements go out automatically on the 5th of each month. Send ad hoc only when a customer asks for a copy, or when a Collections Officer must give updated balance information. Differs from the draft: adds the monthly run and limits the guide to ad hoc sends. (230 §1)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>Statement Distribution VG-18</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1164,16 +1203,21 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>Favorites VG-31</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1208,16 +1252,21 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>Personalized Views VG-22</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1252,16 +1301,21 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>Aged Balances VG-15</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1296,16 +1350,21 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>Customer Invoices VG-14</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1340,16 +1399,21 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>Export to Excel VG-13</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="I19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1384,16 +1448,21 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>Notes and Activities VG-15</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="I20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1428,16 +1497,21 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>Legal Entities VG-15</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="I21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1472,16 +1546,21 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>Workspace VG-15</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="I22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1516,16 +1595,21 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>Overdue Customers VG-15</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="I23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1560,16 +1644,21 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>Customer Account VG-17</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="I24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1604,16 +1693,21 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>Collection Activities VG-17</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="I25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1648,16 +1742,21 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>Statement Preview VG-17</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1692,16 +1791,21 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>Stream O2C (Order-to-Cash), process area Collections, role Collections Officer. The legacy Collections PG also names the Group Billing and Credit Manager in this process area, and files Onboarding and Maintenance, Invoices, Payments and Subscription Billing under the same O2C stream. This differs from the drafts' Accounts Receivable and AR Collections. Source: 230 and 210 Part 1 Stream.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>Statement Distribution VG-19</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="I27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1736,16 +1840,21 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>Favorites VG-33</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1780,16 +1889,21 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>Personalized Views VG-23</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1824,16 +1938,21 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>Aged Balances VG-16</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="I30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1868,16 +1987,21 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
           <t>Customer Invoices VG-15</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1912,16 +2036,21 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>Export to Excel VG-14</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="I32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1956,16 +2085,21 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>Notes and Activities VG-16</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="I33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2000,16 +2134,21 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>Legal Entities VG-16</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2044,16 +2183,21 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>Workspace VG-16</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2088,16 +2232,21 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>Overdue Customers VG-16</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2132,16 +2281,21 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>Customer Account VG-18</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="I37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2176,16 +2330,21 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>Collection Activities VG-18</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="I38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2220,16 +2379,21 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>Statement Preview VG-18</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="I39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2264,16 +2428,21 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>Christoper Clarke, the BPO on every version of the legacy Collections PG (2.0 to 2.3) and on the Subscription Billing PG. Both version histories spell the name this way: please confirm the spelling. Source: 230 and 211 version history.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
           <t>Statement Distribution VG-20</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2306,18 +2475,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Favorites VG-32</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2350,18 +2520,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Personalized Views VG-20</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2394,18 +2565,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Aged Balances VG-18</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="I43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2438,18 +2610,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Customer Invoices VG-17</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="I44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2482,18 +2655,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-16</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2526,18 +2700,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Notes and Activities VG-18</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="I46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2570,18 +2745,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Legal Entities VG-18</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="I47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2614,18 +2790,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Workspace VG-18</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2658,18 +2835,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-18</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="I49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2702,18 +2880,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Customer Account VG-20</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="I50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2746,18 +2925,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Collection Activities VG-20</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="I51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2790,18 +2970,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-20</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="I52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2834,18 +3015,19 @@
           <t>Reports for this process are pending SME confirmation.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Statement Distribution VG-22</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2878,18 +3060,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Favorites VG-17</t>
         </is>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="I54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2922,18 +3105,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Personalized Views VG-25</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="I55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2966,18 +3150,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Aged Balances VG-19</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="I56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3010,18 +3195,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Customer Invoices VG-18</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="I57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3054,18 +3240,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-17</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="I58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3098,18 +3285,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Notes and Activities VG-19</t>
         </is>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="I59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3142,18 +3330,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Legal Entities VG-19</t>
         </is>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="I60" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3186,18 +3375,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Workspace VG-19</t>
         </is>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="I61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3230,18 +3420,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-19</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3274,18 +3465,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Customer Account VG-21</t>
         </is>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3318,18 +3510,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Collection Activities VG-21</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3362,18 +3555,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-21</t>
         </is>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="I65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3406,18 +3600,19 @@
           <t>Access to D365 and to the pages the guide uses (PROCESS START).</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Statement Distribution VG-23</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="I66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3450,18 +3645,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Favorites VG-25</t>
         </is>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="I67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3494,18 +3690,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Personalized Views VG-26</t>
         </is>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="I68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3538,18 +3735,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Aged Balances VG-20</t>
         </is>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="I69" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3582,18 +3780,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Customer Invoices VG-19</t>
         </is>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3626,18 +3825,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-18</t>
         </is>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="I71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3670,18 +3870,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Notes and Activities VG-20</t>
         </is>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="I72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3714,18 +3915,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Legal Entities VG-20</t>
         </is>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="I73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3758,18 +3960,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Workspace VG-20</t>
         </is>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="I74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3802,18 +4005,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-20</t>
         </is>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="I75" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3846,18 +4050,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Customer Account VG-22</t>
         </is>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3890,18 +4095,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Collection Activities VG-22</t>
         </is>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="I77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3934,18 +4140,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-22</t>
         </is>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="I78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3978,18 +4185,19 @@
           <t>Not yet assigned.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Statement Distribution VG-24</t>
         </is>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="I79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4022,18 +4230,19 @@
           <t>Recording timestamps for the views demonstration. These are needed for frame review and screenshots.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Personalized Views VG-27</t>
         </is>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="I80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4066,18 +4275,19 @@
           <t>Recording timestamps for the Aged balances demonstration.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Aged Balances VG-21</t>
         </is>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4110,18 +4320,19 @@
           <t>Recording timestamps for the invoice demonstration.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Customer Invoices VG-20</t>
         </is>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4154,18 +4365,19 @@
           <t>Recording timestamps for the export demonstration.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-19</t>
         </is>
       </c>
-      <c r="H83" s="2" t="n">
+      <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4198,18 +4410,19 @@
           <t>Recording timestamps for the Notes and activities demonstration.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Notes and Activities VG-21</t>
         </is>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4242,18 +4455,19 @@
           <t>Recording timestamps for the legal entity demonstration.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Legal Entities VG-21</t>
         </is>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4286,18 +4500,19 @@
           <t>Recording timestamps for the workspace walkthrough. The Navigation Pane explanation is at about 00:32:42 (source 3.2).</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Workspace VG-21</t>
         </is>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="I86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4330,18 +4545,19 @@
           <t>Recording timestamps for the Customers overdue demonstration.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-21</t>
         </is>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4374,18 +4590,19 @@
           <t>Recording timestamps for the customer account demonstration.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Customer Account VG-23</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4418,18 +4635,19 @@
           <t>Recording timestamps for the activity demonstration.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Collection Activities VG-23</t>
         </is>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4462,18 +4680,19 @@
           <t>Recording timestamps for the statement demonstration.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-23</t>
         </is>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4506,18 +4725,19 @@
           <t>Recording timestamps for the statement demonstration.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Statement Distribution VG-25</t>
         </is>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4550,18 +4770,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-010. The authoring guide requires an assigned code (NNN-Guide Title PG vX.docx).</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Favorites VG-22</t>
         </is>
       </c>
-      <c r="H92" s="2" t="n">
+      <c r="I92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4594,18 +4815,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-004.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="n"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Personalized Views VG-24</t>
         </is>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="I93" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4638,18 +4860,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-007.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Aged Balances VG-17</t>
         </is>
       </c>
-      <c r="H94" s="2" t="n">
+      <c r="I94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4682,18 +4905,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-016.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="n"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Customer Invoices VG-16</t>
         </is>
       </c>
-      <c r="H95" s="2" t="n">
+      <c r="I95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4726,18 +4950,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-019 Export D365 Customer Data to Excel; source 2 uses "Export all rows from a D365 grid".</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-15</t>
         </is>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="I96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4770,18 +4995,19 @@
           <t>Guide code and final title, and whether notes and activities stay in one guide. Source 0 proposes PG-AR-008 and PG-AR-022.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Notes and Activities VG-17</t>
         </is>
       </c>
-      <c r="H97" s="2" t="n">
+      <c r="I97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4814,18 +5040,19 @@
           <t>Guide code and final title. Source 0 gives no code; source 2 uses "Switch to the required legal entity in D365".</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Legal Entities VG-17</t>
         </is>
       </c>
-      <c r="H98" s="2" t="n">
+      <c r="I98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4858,18 +5085,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-001 Navigate and Interpret the Customer Credit &amp; Collections Workspace.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="n"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Workspace VG-17</t>
         </is>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="I99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4902,18 +5130,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-002 Review and Manage Overdue Customers.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-17</t>
         </is>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="I100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4946,18 +5175,19 @@
           <t>Guide code and final title, and whether source 0's three suggested guides (PG-AR-005, -015, -017) stay combined here.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="n"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Customer Account VG-19</t>
         </is>
       </c>
-      <c r="H101" s="2" t="n">
+      <c r="I101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4990,18 +5220,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-003 Record Collection Activities Against a Customer.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Collection Activities VG-19</t>
         </is>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="I102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5034,18 +5265,19 @@
           <t>Guide code and final title, and whether preview and send are separate guides (source 0 proposes one: PG-AR-018).</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-19</t>
         </is>
       </c>
-      <c r="H103" s="2" t="n">
+      <c r="I103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5078,18 +5310,19 @@
           <t>Guide code and final title. Source 0 proposes PG-AR-018 Generate and Send Customer Statements.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Statement Distribution VG-21</t>
         </is>
       </c>
-      <c r="H104" s="2" t="n">
+      <c r="I104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5124,16 +5357,21 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
+          <t>For Favorites VG-16: Yes. Every legacy PG sends users to the D365 issue form on the Atlas D365 User Support Hub ("the fastest way to get help"). The legacy wording limits it to "go-live and early adoption", so confirm the route still applies. Favorites VG-26 (environment and sign-in) is not covered. Source: 230 and 200 Additional Resources.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
           <t>Favorites VG-16; Favorites VG-26</t>
         </is>
       </c>
-      <c r="H105" s="2" t="n">
+      <c r="I105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5166,18 +5404,19 @@
           <t>Every screenshot register requires mock or masked data; no policy is confirmed. No figures are in the Word guides yet.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Favorites VG-27; Workspace VG-22</t>
         </is>
       </c>
-      <c r="H106" s="2" t="n">
+      <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5210,18 +5449,19 @@
           <t>Stated as a Key concept rule in four guides. Source 1 records it as a critical control from the Aged balances demonstration.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Aged Balances VG-13; Customer Invoices VG-12; Export to Excel VG-09; Statement Preview VG-15</t>
         </is>
       </c>
-      <c r="H107" s="2" t="n">
+      <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5254,18 +5494,19 @@
           <t>The Export guide says limits apply but states no figure, and asks users to follow the approved data handling rules.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="n"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-06; Export to Excel VG-08; Export to Excel VG-11</t>
         </is>
       </c>
-      <c r="H108" s="2" t="n">
+      <c r="I108" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5300,16 +5541,21 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
+          <t>After + New, the user picks an activity type, each with its own use: Action (a follow-up that has happened, such as a call or reminder), Appointment (a future call or meeting), Event (a general update or collection milestone) and Task (an internal reminder, such as checking status next week). The interaction goes in a separate Type field, for example Phone call. This differs from the draft, which treats email or phone as the activity type. Source: 230 Key concepts; §5 steps 6 to 7.</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
           <t>Collection Activities VG-05; Collection Activities VG-06</t>
         </is>
       </c>
-      <c r="H109" s="2" t="n">
+      <c r="I109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -5342,18 +5588,19 @@
           <t>No mandatory or prohibited content is stated. Source 1 lists a collection-note standard with examples as still to be written.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Collection Activities VG-09; Collection Activities VG-10; Collection Activities VG-11; Collection Activities VG-24</t>
         </is>
       </c>
-      <c r="H110" s="2" t="n">
+      <c r="I110" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5386,18 +5633,19 @@
           <t>Stated as a Key concept rule in two guides, from the trainer's preference in source 1.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="n"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Notes and Activities VG-11; Collection Activities VG-14</t>
         </is>
       </c>
-      <c r="H111" s="2" t="n">
+      <c r="I111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -5430,18 +5678,19 @@
           <t>Draft: balance due is the total outstanding balance; the overdue amount is the part past its due date.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-04</t>
         </is>
       </c>
-      <c r="H112" s="2" t="n">
+      <c r="I112" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5474,18 +5723,19 @@
           <t>Draft: check which transactions make up the overdue amount, check low-value balances for fees or overpayments, and contact the customer only when the balance is valid.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-08; Overdue Customers VG-09; Overdue Customers VG-10; Customer Account VG-15</t>
         </is>
       </c>
-      <c r="H113" s="2" t="n">
+      <c r="I113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5518,18 +5768,19 @@
           <t>No order or escalation timing is given in the guides.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-11; Overdue Customers VG-13</t>
         </is>
       </c>
-      <c r="H114" s="2" t="n">
+      <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -5564,16 +5815,21 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
+          <t>The label is Use print management destination (a toggle). Set to Yes, it applies the print management settings configured for the customer and sends the output automatically, so a preview must leave it off. Recipients are the customer's email contacts with Purpose = Business on the Contact information FastTab, synchronized with CargoWise; the Primary contact is the default. Only Business contacts receive statements, invoices and collection letters, and changing a contact's Purpose removes it through the integration. Source: 230 §1 step 4, §6.2 step 11, Key concepts, §2.3; 200 §3.4.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
           <t>Statement Preview VG-05; Statement Distribution VG-05; Statement Distribution VG-06</t>
         </is>
       </c>
-      <c r="H115" s="2" t="n">
+      <c r="I115" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5608,16 +5864,21 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
+          <t>The legacy ad hoc statement sets Use print management destination = Yes, Date interval (for example Current year, or From and To dates), Only open = Yes, Balance other than zero = Yes and Include company logo = Yes. The customer goes in Records to include (Filter, then the account in Criteria); left blank, the statement runs for all customers. The statement then runs as a batch job: Batch processing = Yes, a Recurrence start time in the future (+1 hour), and Maximum retries = 0 on the batch task, because otherwise "the system will send multiple copies to the customer". Statements also go out automatically on the 5th of each month. The drafts have none of Date interval, Balance other than zero, the batch settings or the blank-filter warning. Source: 230 §1 steps 4 to 19.</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
           <t>Statement Preview VG-03; Statement Preview VG-04; Statement Distribution VG-03; Statement Distribution VG-04; Statement Distribution VG-17</t>
         </is>
       </c>
-      <c r="H116" s="2" t="n">
+      <c r="I116" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5650,18 +5911,19 @@
           <t>The send guide asks users to check this before sending but cannot say how.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="n"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-13; Statement Distribution VG-12; Statement Distribution VG-13</t>
         </is>
       </c>
-      <c r="H117" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -5694,18 +5956,19 @@
           <t>The send guide names these checks but cannot describe them.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Statement Distribution VG-09; Statement Distribution VG-10; Statement Distribution VG-11</t>
         </is>
       </c>
-      <c r="H118" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5738,18 +6001,19 @@
           <t>Not stated in the guides.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Statement Distribution VG-15; Statement Distribution VG-16; Statement Preview VG-08</t>
         </is>
       </c>
-      <c r="H119" s="2" t="n">
+      <c r="I119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5784,16 +6048,21 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
+          <t>For Customer Invoices VG-21: A Collections Officer resends an invoice from the customer record: Invoice &gt; Journals &gt; Tax invoice journal, select the invoice, Document &gt; Send &gt; Copy, check Print management (delivery method and recipient), then OK. The first send belongs to Billing (License Management Administrator). The other B6 items are not covered. Source: 230 §6.1; 210 §1.4.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
           <t>Customer Invoices VG-06; Customer Invoices VG-08; Customer Invoices VG-09; Customer Invoices VG-11; Customer Invoices VG-21; Statement Preview VG-10; Statement Preview VG-11</t>
         </is>
       </c>
-      <c r="H120" s="2" t="n">
+      <c r="I120" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5828,16 +6097,21 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
+          <t>For Legal Entities VG-10: Every legacy procedure opens with the same control: Check the Entity: "Confirm you are signed into the correct Legal Entity (top-right)." The owner is not stated, and the other B7 items are not covered. Source: all legacy PGs, step 1.</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
           <t>Legal Entities VG-06; Legal Entities VG-07; Legal Entities VG-08; Legal Entities VG-09; Legal Entities VG-10; Legal Entities VG-13; Legal Entities VG-22</t>
         </is>
       </c>
-      <c r="H121" s="2" t="n">
+      <c r="I121" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -5870,18 +6144,19 @@
           <t>The Notes guide names statements and collection letters as examples only.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Notes and Activities VG-05; Notes and Activities VG-06; Notes and Activities VG-12; Collection Activities VG-15</t>
         </is>
       </c>
-      <c r="H122" s="2" t="n">
+      <c r="I122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5916,16 +6191,21 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
+          <t>For Customer Account VG-03: Yes for Aged balances: the legacy monitoring task clicks the customer Name in Aged balances to open the customer's Collections page and review Open transactions. The legacy PGs do not use Customers overdue. This bears on decision D2.1, whose default keeps opening a customer out of the Aged Balances guide. The other B9 items are not covered. Source: 230 §2.1 steps 5 to 6.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
           <t>Aged Balances VG-09; Customer Account VG-08; Customer Account VG-12; Customer Account VG-03</t>
         </is>
       </c>
-      <c r="H123" s="2" t="n">
+      <c r="I123" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr"/>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5958,18 +6238,19 @@
           <t>The guide names Customers overdue, Payment journals not posted, Notes and Open payment journals as used, and lists others without saying whether they are used.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Workspace VG-08; Workspace VG-09</t>
         </is>
       </c>
-      <c r="H124" s="2" t="n">
+      <c r="I124" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -6004,16 +6285,21 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
+          <t>For Favorites VG-18: Collections uses Customer payment journal (CPJL) to transfer open or closed payments between customer accounts when a payment is on the wrong account. Receipting also uses it for payments automated settlement can't process: cheques and failed imports, backdated adjustments, parent-child batch payments, payments across several accounts and intercompany transfers. This matches the Part 2 notes. The other B11 items are not covered. Source: 230 §6.7; 220 §4.</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
           <t>Favorites VG-18; Favorites VG-20; Personalized Views VG-01; Personalized Views VG-12; Personalized Views VG-19; Personalized Views VG-28; Aged Balances VG-22</t>
         </is>
       </c>
-      <c r="H125" s="2" t="n">
+      <c r="I125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -6046,18 +6332,19 @@
           <t>Both are inferences in the drafts.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Aged Balances VG-08; Favorites VG-19</t>
         </is>
       </c>
-      <c r="H126" s="2" t="n">
+      <c r="I126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -6090,18 +6377,19 @@
           <t>Opening a customer from Aged balances belongs in the Investigate a customer account guide, not the Aged Balances guide.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="n"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Aged Balances VG-23</t>
         </is>
       </c>
-      <c r="H127" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6134,18 +6422,19 @@
           <t>Undo settlement stays out of the Customer Account guide (higher-risk; its own gated guide).</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Customer Account VG-13</t>
         </is>
       </c>
-      <c r="H128" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6178,18 +6467,19 @@
           <t>The custom all-customer transaction report is a separate guide, once its access path is captured.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Customer Account VG-24</t>
         </is>
       </c>
-      <c r="H129" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -6222,18 +6512,19 @@
           <t>The custom all-customer transaction report and daily bank statements are separate guides.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-20</t>
         </is>
       </c>
-      <c r="H130" s="2" t="n">
+      <c r="I130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -6266,18 +6557,19 @@
           <t>The Export guide opens "the page that holds the data" instead of one fixed Modules/Navigate path.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="n"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Export to Excel VG-10</t>
         </is>
       </c>
-      <c r="H131" s="2" t="n">
+      <c r="I131" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6310,18 +6602,19 @@
           <t>Finding an invoice with Show closed or Hide FX revaluations belongs in the transactions guide, not the Invoices guide.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="n"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Customer Invoices VG-22</t>
         </is>
       </c>
-      <c r="H132" s="2" t="n">
+      <c r="I132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -6354,18 +6647,19 @@
           <t>Recording a new activity belongs in the Record a collection activity guide.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Notes and Activities VG-22</t>
         </is>
       </c>
-      <c r="H133" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -6398,18 +6692,19 @@
           <t>Recording the contact and using the email address belong in the Record a collection activity guide.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Overdue Customers VG-23</t>
         </is>
       </c>
-      <c r="H134" s="2" t="n">
+      <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -6442,18 +6737,19 @@
           <t>Sending a statement is covered by the Generate and send a customer statement guide, not the preview guide.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="n"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-24</t>
         </is>
       </c>
-      <c r="H135" s="2" t="n">
+      <c r="I135" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6486,18 +6782,19 @@
           <t>Statements for multiple related accounts are out of the Statement Preview guide (source 1: partial).</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G136" s="2" t="n"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Statement Preview VG-14</t>
         </is>
       </c>
-      <c r="H136" s="2" t="n">
+      <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -6530,18 +6827,19 @@
           <t>Statements for multiple related accounts are out of the Statement Distribution guide (source 1: partial).</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" s="2" t="n"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Statement Distribution VG-14</t>
         </is>
       </c>
-      <c r="H137" s="2" t="n">
+      <c r="I137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -6574,21 +6872,22 @@
           <t>Workspace indicators belong in a separate system overview, not the Workspace guide.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="n"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Workspace VG-13</t>
         </is>
       </c>
-      <c r="H138" s="2" t="n">
+      <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L138"/>
+  <autoFilter ref="A1:M138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -6600,7 +6899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6610,6 +6909,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6648,6 +6948,11 @@
           <t>Closed (Yes / No)</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Legacy PG proposal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6681,6 +6986,11 @@
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6714,6 +7024,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6747,6 +7058,11 @@
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6780,6 +7096,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6813,6 +7130,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6846,6 +7164,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6879,6 +7198,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -6912,6 +7232,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6945,6 +7266,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -6978,6 +7300,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7011,6 +7334,11 @@
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7044,6 +7372,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7077,6 +7406,11 @@
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -7110,6 +7444,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7143,6 +7478,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -7176,6 +7512,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -7209,6 +7546,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -7242,6 +7580,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -7275,6 +7614,11 @@
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -7308,6 +7652,11 @@
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -7341,6 +7690,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -7374,6 +7724,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -7407,6 +7758,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -7440,6 +7792,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -7473,6 +7826,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -7506,6 +7860,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -7539,6 +7894,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -7572,6 +7928,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -7605,6 +7962,11 @@
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -7638,6 +8000,11 @@
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -7671,6 +8038,11 @@
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -7704,6 +8076,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -7737,6 +8110,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7770,6 +8144,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7803,6 +8178,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7836,6 +8212,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7869,6 +8246,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7902,6 +8280,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7935,6 +8314,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7968,6 +8348,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8382,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8034,6 +8416,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8067,6 +8450,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8100,6 +8484,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8133,6 +8518,11 @@
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8166,6 +8556,11 @@
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8199,6 +8594,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -8232,6 +8628,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -8265,6 +8662,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -8298,6 +8696,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -8331,6 +8730,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -8364,6 +8764,11 @@
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -8397,6 +8802,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -8430,6 +8836,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -8463,6 +8870,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -8496,6 +8904,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -8529,6 +8938,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -8562,6 +8972,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -8595,6 +9006,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -8628,6 +9040,11 @@
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -8661,6 +9078,11 @@
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -8694,6 +9116,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -8727,6 +9150,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -8760,6 +9184,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -8793,6 +9218,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -8826,6 +9252,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -8859,6 +9286,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -8892,6 +9320,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8925,6 +9354,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -8958,6 +9388,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -8991,6 +9422,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -9024,6 +9456,11 @@
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -9057,6 +9494,11 @@
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -9090,6 +9532,11 @@
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -9123,6 +9570,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -9156,6 +9604,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -9189,6 +9638,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -9222,6 +9672,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -9255,6 +9706,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -9288,6 +9740,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -9321,6 +9774,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -9354,6 +9808,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -9387,6 +9842,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -9420,6 +9876,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -9453,6 +9910,11 @@
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -9486,6 +9948,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -9519,6 +9982,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -9552,6 +10016,11 @@
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -9585,6 +10054,11 @@
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -9618,6 +10092,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -9651,6 +10126,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -9684,6 +10160,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -9717,6 +10194,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -9750,6 +10228,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -9783,6 +10262,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -9816,6 +10296,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -9849,6 +10330,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -9882,6 +10364,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -9915,6 +10398,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -9948,6 +10432,11 @@
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -9981,6 +10470,11 @@
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -10014,6 +10508,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -10047,6 +10542,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -10080,6 +10576,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -10113,6 +10610,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -10146,6 +10644,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -10179,6 +10678,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -10212,6 +10712,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -10245,6 +10746,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -10278,6 +10780,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -10311,6 +10814,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -10344,6 +10848,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -10377,6 +10882,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -10410,6 +10916,11 @@
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -10443,6 +10954,11 @@
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -10476,6 +10992,11 @@
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -10509,6 +11030,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -10542,6 +11064,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -10575,6 +11098,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -10608,6 +11132,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -10641,6 +11166,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -10674,6 +11200,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -10707,6 +11234,11 @@
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -10740,6 +11272,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -10773,6 +11306,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -10806,6 +11340,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -10839,6 +11374,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -10872,6 +11408,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -10905,6 +11442,11 @@
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -10938,6 +11480,11 @@
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -10971,6 +11518,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -11004,6 +11552,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -11037,6 +11586,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -11070,6 +11620,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -11103,6 +11654,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -11136,6 +11688,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -11169,6 +11722,11 @@
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -11202,6 +11760,11 @@
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -11235,6 +11798,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -11268,6 +11832,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -11301,6 +11866,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -11334,6 +11900,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -11367,6 +11934,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -11400,6 +11968,11 @@
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -11433,6 +12006,11 @@
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -11466,6 +12044,11 @@
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -11499,6 +12082,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -11532,6 +12116,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -11565,6 +12150,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -11598,6 +12184,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -11631,6 +12218,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -11664,6 +12252,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -11697,6 +12286,11 @@
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -11730,6 +12324,11 @@
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -11763,6 +12362,11 @@
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -11796,6 +12400,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -11829,6 +12434,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -11862,6 +12468,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -11895,6 +12502,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -11928,6 +12536,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -11961,6 +12570,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -11994,6 +12604,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -12027,6 +12638,11 @@
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -12060,6 +12676,11 @@
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -12093,6 +12714,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -12126,6 +12748,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -12159,6 +12782,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -12192,6 +12816,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -12225,6 +12850,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -12258,6 +12884,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -12291,6 +12918,11 @@
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -12324,6 +12956,11 @@
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -12357,6 +12994,11 @@
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -12390,6 +13032,11 @@
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -12423,6 +13070,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -12456,6 +13104,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -12489,6 +13138,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -12522,6 +13172,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -12555,6 +13206,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -12588,6 +13240,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -12621,6 +13274,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -12654,6 +13308,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -12687,6 +13342,11 @@
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -12720,6 +13380,11 @@
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -12753,6 +13418,11 @@
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -12786,6 +13456,11 @@
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -12819,6 +13494,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -12852,6 +13528,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -12885,6 +13562,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -12918,6 +13596,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -12951,9 +13630,10 @@
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G192"/>
+  <autoFilter ref="A1:H192"/>
   <dataValidations count="1">
     <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,Partly"</formula1>
